--- a/artfynd/A 14184-2026 artfynd.xlsx
+++ b/artfynd/A 14184-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY145"/>
+  <dimension ref="A1:AZ145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757031</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757076</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757186</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757074</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,6 +1307,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757075</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1407,6 +1437,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757184</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1532,6 +1567,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757182</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1662,6 +1702,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757183</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1787,6 +1832,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757166</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1912,6 +1962,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757033</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2037,6 +2092,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757034</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2162,6 +2222,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757035</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2287,6 +2352,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757036</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2412,6 +2482,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757037</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2537,6 +2612,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757038</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2662,6 +2742,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757039</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2787,6 +2872,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757040</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2912,6 +3002,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757041</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3037,6 +3132,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757042</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3162,6 +3262,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757043</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3287,6 +3392,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757044</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3412,6 +3522,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757045</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3533,6 +3648,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757178</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3654,6 +3774,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757179</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3775,6 +3900,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757180</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3896,6 +4026,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757181</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4017,6 +4152,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757096</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4138,6 +4278,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757097</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4259,6 +4404,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757098</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4380,6 +4530,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757082</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4501,6 +4656,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757083</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4622,6 +4782,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757084</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4743,6 +4908,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757085</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4864,6 +5034,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757086</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4974,6 +5149,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757032</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5095,6 +5275,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757169</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5201,6 +5386,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757171</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5322,6 +5512,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757173</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5428,6 +5623,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757174</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5549,6 +5749,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757175</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5670,6 +5875,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757176</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5791,6 +6001,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757177</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5912,6 +6127,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757095</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6033,6 +6253,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757026</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6154,6 +6379,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757027</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6275,6 +6505,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757029</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6396,6 +6631,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757030</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6517,6 +6757,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757151</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6638,6 +6883,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757152</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6759,6 +7009,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757154</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6880,6 +7135,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757155</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7001,6 +7261,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757156</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7122,6 +7387,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757158</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7243,6 +7513,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757159</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7364,6 +7639,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757087</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7485,6 +7765,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757088</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7606,6 +7891,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757089</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7727,6 +8017,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757090</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7848,6 +8143,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757091</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7969,6 +8269,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757092</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8090,6 +8395,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757093</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8211,6 +8521,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757094</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8332,6 +8647,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757099</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8453,6 +8773,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757100</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8574,6 +8899,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757101</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8704,6 +9034,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757102</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8825,6 +9160,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757103</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8946,6 +9286,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757104</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9067,6 +9412,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757105</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9188,6 +9538,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757106</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9309,6 +9664,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757107</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9430,6 +9790,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757108</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9551,6 +9916,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757109</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9672,6 +10042,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757110</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9793,6 +10168,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757112</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9923,6 +10303,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757113</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10044,6 +10429,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757114</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10165,6 +10555,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757115</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10286,6 +10681,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757116</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10407,6 +10807,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757117</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10528,6 +10933,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757118</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10649,6 +11059,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757119</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10770,6 +11185,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757120</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10891,6 +11311,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757121</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11012,6 +11437,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757122</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11133,6 +11563,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757123</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11259,6 +11694,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757125</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11380,6 +11820,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757126</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11501,6 +11946,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757127</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11636,6 +12086,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757128</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11757,6 +12212,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757129</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11887,6 +12347,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757130</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12018,6 +12483,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757131</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12144,6 +12614,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757132</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12265,6 +12740,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757133</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12386,6 +12866,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757134</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12507,6 +12992,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757135</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12628,6 +13118,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757136</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12749,6 +13244,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757137</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12870,6 +13370,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757138</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12991,6 +13496,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757139</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13112,6 +13622,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757140</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13233,6 +13748,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757141</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13354,6 +13874,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757142</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13475,6 +14000,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757143</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13596,6 +14126,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757144</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13726,6 +14261,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757145</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13847,6 +14387,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757146</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13968,6 +14513,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757147</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -14094,6 +14644,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757189</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14219,6 +14774,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757073</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -14349,6 +14909,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757077</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14467,6 +15032,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757078</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14597,6 +15167,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757048</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14727,6 +15302,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757049</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14857,6 +15437,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757051</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14987,6 +15572,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757052</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -15117,6 +15707,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757053</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -15247,6 +15842,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757054</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -15377,6 +15977,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757055</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -15512,6 +16117,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757056</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15642,6 +16252,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757057</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15772,6 +16387,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757058</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15902,6 +16522,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757059</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -16032,6 +16657,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757060</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -16162,6 +16792,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757062</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -16292,6 +16927,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757063</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -16422,6 +17062,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757064</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -16548,6 +17193,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757065</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -16678,6 +17328,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757066</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16808,6 +17463,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757067</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16938,6 +17598,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757068</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -17068,6 +17733,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757069</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -17190,6 +17860,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757148</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -17314,6 +17989,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757161</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -17438,6 +18118,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757163</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -17562,6 +18247,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757164</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -17673,6 +18363,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757187</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -17784,6 +18479,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757188</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17905,6 +18605,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757149</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -18026,6 +18731,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757150</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -18156,6 +18866,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757070</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -18286,6 +19001,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757071</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -18412,8 +19132,159 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132757185</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>